--- a/demo_cases/files/client_profile_mismatch/base_info.xlsx
+++ b/demo_cases/files/client_profile_mismatch/base_info.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91310000MA1K000001</t>
+          <t>91310115MA1RXH0026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
